--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -3584,10 +3584,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118378113</v>
+        <v>118378086</v>
       </c>
       <c r="B26" t="n">
-        <v>79565</v>
+        <v>78573</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3596,25 +3596,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>389580</v>
+        <v>389615</v>
       </c>
       <c r="R26" t="n">
-        <v>7061470</v>
+        <v>7061456</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>block</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118378115</v>
+        <v>118378085</v>
       </c>
       <c r="B27" t="n">
-        <v>79566</v>
+        <v>74520</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3703,25 +3703,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>389580</v>
+        <v>389631</v>
       </c>
       <c r="R27" t="n">
-        <v>7061470</v>
+        <v>7061464</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3780,7 +3780,12 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3798,10 +3803,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118378106</v>
+        <v>118378113</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3814,21 +3819,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3838,10 +3843,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>389412</v>
+        <v>389580</v>
       </c>
       <c r="R28" t="n">
-        <v>7061456</v>
+        <v>7061470</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3887,7 +3892,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3905,10 +3910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118378085</v>
+        <v>118378027</v>
       </c>
       <c r="B29" t="n">
-        <v>74520</v>
+        <v>74596</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3917,25 +3922,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1461</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3945,10 +3950,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>389631</v>
+        <v>389582</v>
       </c>
       <c r="R29" t="n">
-        <v>7061464</v>
+        <v>7061446</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3975,12 +3980,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3994,12 +4004,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>lodyta</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4017,10 +4022,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118378024</v>
+        <v>118378088</v>
       </c>
       <c r="B30" t="n">
-        <v>74594</v>
+        <v>74591</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4029,20 +4034,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6486</v>
+        <v>310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4057,10 +4062,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>389551</v>
+        <v>389534</v>
       </c>
       <c r="R30" t="n">
-        <v>7061475</v>
+        <v>7061458</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4087,12 +4092,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4106,7 +4111,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4124,10 +4129,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118378027</v>
+        <v>118378021</v>
       </c>
       <c r="B31" t="n">
-        <v>74596</v>
+        <v>80140</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4136,25 +4141,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>735</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4164,10 +4169,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>389582</v>
+        <v>389551</v>
       </c>
       <c r="R31" t="n">
-        <v>7061446</v>
+        <v>7061475</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4202,11 +4207,6 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4236,10 +4236,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118378111</v>
+        <v>118378020</v>
       </c>
       <c r="B32" t="n">
-        <v>78647</v>
+        <v>74528</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4252,21 +4252,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1249</v>
+        <v>1776</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>389580</v>
+        <v>389551</v>
       </c>
       <c r="R32" t="n">
-        <v>7061470</v>
+        <v>7061475</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118378021</v>
+        <v>118378115</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>79566</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4355,25 +4355,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>735</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>389551</v>
+        <v>389580</v>
       </c>
       <c r="R33" t="n">
-        <v>7061475</v>
+        <v>7061470</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4413,12 +4413,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4450,10 +4450,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118378022</v>
+        <v>118378106</v>
       </c>
       <c r="B34" t="n">
-        <v>74408</v>
+        <v>78484</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4462,25 +4462,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>389551</v>
+        <v>389412</v>
       </c>
       <c r="R34" t="n">
-        <v>7061475</v>
+        <v>7061456</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4520,12 +4520,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118378112</v>
+        <v>118378111</v>
       </c>
       <c r="B35" t="n">
-        <v>79601</v>
+        <v>78647</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,25 +4569,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118378086</v>
+        <v>118378108</v>
       </c>
       <c r="B36" t="n">
-        <v>78573</v>
+        <v>80140</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4676,25 +4676,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6450</v>
+        <v>735</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>389615</v>
+        <v>389432</v>
       </c>
       <c r="R36" t="n">
-        <v>7061456</v>
+        <v>7061449</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4750,11 +4750,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>block</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4771,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118378088</v>
+        <v>118378028</v>
       </c>
       <c r="B37" t="n">
-        <v>74591</v>
+        <v>77421</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4787,21 +4782,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>310</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4811,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>389534</v>
+        <v>389582</v>
       </c>
       <c r="R37" t="n">
-        <v>7061458</v>
+        <v>7061446</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4841,12 +4836,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4878,10 +4878,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118378108</v>
+        <v>118378022</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>74408</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4890,25 +4890,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>735</v>
+        <v>6428</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>389432</v>
+        <v>389551</v>
       </c>
       <c r="R38" t="n">
-        <v>7061449</v>
+        <v>7061475</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4964,6 +4964,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4980,10 +4985,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118378028</v>
+        <v>118378112</v>
       </c>
       <c r="B39" t="n">
-        <v>77421</v>
+        <v>79601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4992,25 +4997,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5020,10 +5025,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>389582</v>
+        <v>389580</v>
       </c>
       <c r="R39" t="n">
-        <v>7061446</v>
+        <v>7061470</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5050,17 +5055,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118378020</v>
+        <v>118378024</v>
       </c>
       <c r="B40" t="n">
-        <v>74528</v>
+        <v>74594</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5108,21 +5108,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1776</v>
+        <v>6486</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -3584,10 +3584,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118378086</v>
+        <v>118378111</v>
       </c>
       <c r="B26" t="n">
-        <v>78573</v>
+        <v>78647</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3596,25 +3596,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6450</v>
+        <v>1249</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>389615</v>
+        <v>389580</v>
       </c>
       <c r="R26" t="n">
-        <v>7061456</v>
+        <v>7061470</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118378085</v>
+        <v>118378115</v>
       </c>
       <c r="B27" t="n">
-        <v>74520</v>
+        <v>79566</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3703,25 +3703,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1461</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>389631</v>
+        <v>389580</v>
       </c>
       <c r="R27" t="n">
-        <v>7061464</v>
+        <v>7061470</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3780,12 +3780,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>lodyta</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3803,10 +3798,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118378113</v>
+        <v>118378021</v>
       </c>
       <c r="B28" t="n">
-        <v>79565</v>
+        <v>80140</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3815,25 +3810,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3843,10 +3838,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>389580</v>
+        <v>389551</v>
       </c>
       <c r="R28" t="n">
-        <v>7061470</v>
+        <v>7061475</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3873,12 +3868,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3892,7 +3887,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3910,10 +3905,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118378027</v>
+        <v>118378020</v>
       </c>
       <c r="B29" t="n">
-        <v>74596</v>
+        <v>74528</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3922,25 +3917,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1776</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3950,10 +3945,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>389582</v>
+        <v>389551</v>
       </c>
       <c r="R29" t="n">
-        <v>7061446</v>
+        <v>7061475</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3988,11 +3983,6 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4004,7 +3994,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4022,10 +4012,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118378088</v>
+        <v>118378108</v>
       </c>
       <c r="B30" t="n">
-        <v>74591</v>
+        <v>80140</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4034,25 +4024,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>310</v>
+        <v>735</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4062,10 +4052,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>389534</v>
+        <v>389432</v>
       </c>
       <c r="R30" t="n">
-        <v>7061458</v>
+        <v>7061449</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4108,11 +4098,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4129,10 +4114,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118378021</v>
+        <v>118378112</v>
       </c>
       <c r="B31" t="n">
-        <v>80140</v>
+        <v>79601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4141,25 +4126,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>735</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4169,10 +4154,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>389551</v>
+        <v>389580</v>
       </c>
       <c r="R31" t="n">
-        <v>7061475</v>
+        <v>7061470</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4199,12 +4184,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4218,7 +4203,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4236,10 +4221,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118378020</v>
+        <v>118378086</v>
       </c>
       <c r="B32" t="n">
-        <v>74528</v>
+        <v>78573</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4248,25 +4233,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1776</v>
+        <v>6450</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4276,10 +4261,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>389551</v>
+        <v>389615</v>
       </c>
       <c r="R32" t="n">
-        <v>7061475</v>
+        <v>7061456</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4306,12 +4291,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4325,7 +4310,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>block</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4343,10 +4328,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118378115</v>
+        <v>118378024</v>
       </c>
       <c r="B33" t="n">
-        <v>79566</v>
+        <v>74594</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4355,25 +4340,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6486</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4383,10 +4368,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>389580</v>
+        <v>389551</v>
       </c>
       <c r="R33" t="n">
-        <v>7061470</v>
+        <v>7061475</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4413,12 +4398,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4432,7 +4417,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4450,10 +4435,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118378106</v>
+        <v>118378113</v>
       </c>
       <c r="B34" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4466,21 +4451,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4490,10 +4475,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>389412</v>
+        <v>389580</v>
       </c>
       <c r="R34" t="n">
-        <v>7061456</v>
+        <v>7061470</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4539,7 +4524,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4557,10 +4542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118378111</v>
+        <v>118378027</v>
       </c>
       <c r="B35" t="n">
-        <v>78647</v>
+        <v>74596</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,25 +4554,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4597,10 +4582,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>389580</v>
+        <v>389582</v>
       </c>
       <c r="R35" t="n">
-        <v>7061470</v>
+        <v>7061446</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4627,12 +4612,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4646,7 +4636,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4664,10 +4654,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118378108</v>
+        <v>118378028</v>
       </c>
       <c r="B36" t="n">
-        <v>80140</v>
+        <v>77421</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4676,25 +4666,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>735</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>389432</v>
+        <v>389582</v>
       </c>
       <c r="R36" t="n">
-        <v>7061449</v>
+        <v>7061446</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4734,12 +4724,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4750,6 +4745,11 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118378028</v>
+        <v>118378088</v>
       </c>
       <c r="B37" t="n">
-        <v>77421</v>
+        <v>74591</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>389582</v>
+        <v>389534</v>
       </c>
       <c r="R37" t="n">
-        <v>7061446</v>
+        <v>7061458</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4836,17 +4836,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4985,10 +4980,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118378112</v>
+        <v>118378085</v>
       </c>
       <c r="B39" t="n">
-        <v>79601</v>
+        <v>74520</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4997,25 +4992,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>1461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5025,10 +5020,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>389580</v>
+        <v>389631</v>
       </c>
       <c r="R39" t="n">
-        <v>7061470</v>
+        <v>7061464</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5074,7 +5069,12 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118378024</v>
+        <v>118378106</v>
       </c>
       <c r="B40" t="n">
-        <v>74594</v>
+        <v>78484</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5104,25 +5104,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>389551</v>
+        <v>389412</v>
       </c>
       <c r="R40" t="n">
-        <v>7061475</v>
+        <v>7061456</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -3584,10 +3584,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118378111</v>
+        <v>118378024</v>
       </c>
       <c r="B26" t="n">
-        <v>78647</v>
+        <v>74601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>389580</v>
+        <v>389551</v>
       </c>
       <c r="R26" t="n">
-        <v>7061470</v>
+        <v>7061475</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118378115</v>
+        <v>118378088</v>
       </c>
       <c r="B27" t="n">
-        <v>79566</v>
+        <v>74598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>389580</v>
+        <v>389534</v>
       </c>
       <c r="R27" t="n">
-        <v>7061470</v>
+        <v>7061458</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118378021</v>
+        <v>118378028</v>
       </c>
       <c r="B28" t="n">
-        <v>80140</v>
+        <v>77428</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3810,25 +3810,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>735</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>389551</v>
+        <v>389582</v>
       </c>
       <c r="R28" t="n">
-        <v>7061475</v>
+        <v>7061446</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3876,6 +3876,11 @@
           <t>2022-07-27</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3887,7 +3892,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3905,10 +3910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118378020</v>
+        <v>118378022</v>
       </c>
       <c r="B29" t="n">
-        <v>74528</v>
+        <v>74415</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3917,25 +3922,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1776</v>
+        <v>6428</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4012,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118378108</v>
+        <v>118378106</v>
       </c>
       <c r="B30" t="n">
-        <v>80140</v>
+        <v>78491</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4024,25 +4029,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>735</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4052,10 +4057,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>389432</v>
+        <v>389412</v>
       </c>
       <c r="R30" t="n">
-        <v>7061449</v>
+        <v>7061456</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4098,6 +4103,11 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4114,10 +4124,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118378112</v>
+        <v>118378108</v>
       </c>
       <c r="B31" t="n">
-        <v>79601</v>
+        <v>80147</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4126,25 +4136,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>735</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4154,10 +4164,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>389580</v>
+        <v>389432</v>
       </c>
       <c r="R31" t="n">
-        <v>7061470</v>
+        <v>7061449</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4200,11 +4210,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4221,10 +4226,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118378086</v>
+        <v>118378085</v>
       </c>
       <c r="B32" t="n">
-        <v>78573</v>
+        <v>74527</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4233,25 +4238,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6450</v>
+        <v>1461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4261,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>389615</v>
+        <v>389631</v>
       </c>
       <c r="R32" t="n">
-        <v>7061456</v>
+        <v>7061464</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4310,7 +4315,12 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4328,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118378024</v>
+        <v>118378115</v>
       </c>
       <c r="B33" t="n">
-        <v>74594</v>
+        <v>79573</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4340,25 +4350,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6486</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4368,10 +4378,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>389551</v>
+        <v>389580</v>
       </c>
       <c r="R33" t="n">
-        <v>7061475</v>
+        <v>7061470</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4398,12 +4408,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4417,7 +4427,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4435,10 +4445,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118378113</v>
+        <v>118378021</v>
       </c>
       <c r="B34" t="n">
-        <v>79565</v>
+        <v>80147</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4447,25 +4457,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>735</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4475,10 +4485,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>389580</v>
+        <v>389551</v>
       </c>
       <c r="R34" t="n">
-        <v>7061470</v>
+        <v>7061475</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4505,12 +4515,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4524,7 +4534,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4542,10 +4552,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118378027</v>
+        <v>118378086</v>
       </c>
       <c r="B35" t="n">
-        <v>74596</v>
+        <v>78580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4554,25 +4564,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6450</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4582,10 +4592,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>389582</v>
+        <v>389615</v>
       </c>
       <c r="R35" t="n">
-        <v>7061446</v>
+        <v>7061456</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4612,17 +4622,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4636,7 +4641,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>block</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4654,10 +4659,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118378028</v>
+        <v>118378112</v>
       </c>
       <c r="B36" t="n">
-        <v>77421</v>
+        <v>79608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4666,25 +4671,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4694,10 +4699,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>389582</v>
+        <v>389580</v>
       </c>
       <c r="R36" t="n">
-        <v>7061446</v>
+        <v>7061470</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4724,17 +4729,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118378088</v>
+        <v>118378111</v>
       </c>
       <c r="B37" t="n">
-        <v>74591</v>
+        <v>78654</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4778,25 +4778,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>310</v>
+        <v>1249</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>389534</v>
+        <v>389580</v>
       </c>
       <c r="R37" t="n">
-        <v>7061458</v>
+        <v>7061470</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118378022</v>
+        <v>118378020</v>
       </c>
       <c r="B38" t="n">
-        <v>74408</v>
+        <v>74535</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4885,25 +4885,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6428</v>
+        <v>1776</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118378085</v>
+        <v>118378113</v>
       </c>
       <c r="B39" t="n">
-        <v>74520</v>
+        <v>79572</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4992,25 +4992,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1461</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>389631</v>
+        <v>389580</v>
       </c>
       <c r="R39" t="n">
-        <v>7061464</v>
+        <v>7061470</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5069,12 +5069,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>lodyta</t>
-        </is>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5092,10 +5087,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118378106</v>
+        <v>118378027</v>
       </c>
       <c r="B40" t="n">
-        <v>78484</v>
+        <v>74603</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5108,21 +5103,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>389412</v>
+        <v>389582</v>
       </c>
       <c r="R40" t="n">
-        <v>7061456</v>
+        <v>7061446</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5162,12 +5157,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -3584,10 +3584,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118378024</v>
+        <v>118378085</v>
       </c>
       <c r="B26" t="n">
-        <v>74601</v>
+        <v>74527</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6486</v>
+        <v>1461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>389551</v>
+        <v>389631</v>
       </c>
       <c r="R26" t="n">
-        <v>7061475</v>
+        <v>7061464</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3673,7 +3673,12 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3798,10 +3803,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118378028</v>
+        <v>118378111</v>
       </c>
       <c r="B28" t="n">
-        <v>77428</v>
+        <v>78654</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3810,25 +3815,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3838,10 +3843,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>389582</v>
+        <v>389580</v>
       </c>
       <c r="R28" t="n">
-        <v>7061446</v>
+        <v>7061470</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3868,17 +3873,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118378022</v>
+        <v>118378113</v>
       </c>
       <c r="B29" t="n">
-        <v>74415</v>
+        <v>79572</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3922,25 +3922,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>389551</v>
+        <v>389580</v>
       </c>
       <c r="R29" t="n">
-        <v>7061475</v>
+        <v>7061470</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3980,12 +3980,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118378106</v>
+        <v>118378112</v>
       </c>
       <c r="B30" t="n">
-        <v>78491</v>
+        <v>79608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4029,25 +4029,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>389412</v>
+        <v>389580</v>
       </c>
       <c r="R30" t="n">
-        <v>7061456</v>
+        <v>7061470</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4124,10 +4124,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118378108</v>
+        <v>118378022</v>
       </c>
       <c r="B31" t="n">
-        <v>80147</v>
+        <v>74415</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4136,25 +4136,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>735</v>
+        <v>6428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>389432</v>
+        <v>389551</v>
       </c>
       <c r="R31" t="n">
-        <v>7061449</v>
+        <v>7061475</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4194,12 +4194,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4210,6 +4210,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4226,10 +4231,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118378085</v>
+        <v>118378021</v>
       </c>
       <c r="B32" t="n">
-        <v>74527</v>
+        <v>80147</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4242,21 +4247,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1461</v>
+        <v>735</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4266,10 +4271,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>389631</v>
+        <v>389551</v>
       </c>
       <c r="R32" t="n">
-        <v>7061464</v>
+        <v>7061475</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4296,12 +4301,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4315,12 +4320,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>lodyta</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118378115</v>
+        <v>118378027</v>
       </c>
       <c r="B33" t="n">
-        <v>79573</v>
+        <v>74603</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4354,21 +4354,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>389580</v>
+        <v>389582</v>
       </c>
       <c r="R33" t="n">
-        <v>7061470</v>
+        <v>7061446</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4408,12 +4408,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4427,7 +4432,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4445,7 +4450,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118378021</v>
+        <v>118378108</v>
       </c>
       <c r="B34" t="n">
         <v>80147</v>
@@ -4485,10 +4490,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>389551</v>
+        <v>389432</v>
       </c>
       <c r="R34" t="n">
-        <v>7061475</v>
+        <v>7061449</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4515,12 +4520,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4531,11 +4536,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>granbas</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118378112</v>
+        <v>118378115</v>
       </c>
       <c r="B36" t="n">
-        <v>79608</v>
+        <v>79573</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,25 +4671,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118378111</v>
+        <v>118378024</v>
       </c>
       <c r="B37" t="n">
-        <v>78654</v>
+        <v>74601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1249</v>
+        <v>6486</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>389580</v>
+        <v>389551</v>
       </c>
       <c r="R37" t="n">
-        <v>7061470</v>
+        <v>7061475</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4836,12 +4836,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118378113</v>
+        <v>118378106</v>
       </c>
       <c r="B39" t="n">
-        <v>79572</v>
+        <v>78491</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4996,21 +4996,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>389580</v>
+        <v>389412</v>
       </c>
       <c r="R39" t="n">
-        <v>7061470</v>
+        <v>7061456</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118378027</v>
+        <v>118378028</v>
       </c>
       <c r="B40" t="n">
-        <v>74603</v>
+        <v>77428</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5103,21 +5103,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,10 +4761,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118378111</v>
+        <v>118378028</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>77430</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,25 +4773,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>389580</v>
+        <v>389582</v>
       </c>
       <c r="R37" t="n">
-        <v>7061470</v>
+        <v>7061446</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4831,12 +4831,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4850,7 +4855,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4868,10 +4873,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118378028</v>
+        <v>118378085</v>
       </c>
       <c r="B38" t="n">
-        <v>77430</v>
+        <v>74529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4880,25 +4885,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>1461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4908,10 +4913,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>389582</v>
+        <v>389631</v>
       </c>
       <c r="R38" t="n">
-        <v>7061446</v>
+        <v>7061464</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4938,17 +4943,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4962,7 +4962,12 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4980,10 +4985,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118378085</v>
+        <v>118378112</v>
       </c>
       <c r="B39" t="n">
-        <v>74529</v>
+        <v>79610</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4992,25 +4997,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1461</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5020,10 +5025,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>389631</v>
+        <v>389580</v>
       </c>
       <c r="R39" t="n">
-        <v>7061464</v>
+        <v>7061470</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5069,12 +5074,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>lodyta</t>
-        </is>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5092,53 +5092,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118378112</v>
+        <v>101621434</v>
       </c>
       <c r="B40" t="n">
-        <v>79610</v>
+        <v>94121</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, N-sidan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>389580</v>
+        <v>390604.1747182368</v>
       </c>
       <c r="R40" t="n">
-        <v>7061470</v>
+        <v>7061513.082409594</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5162,12 +5166,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5176,33 +5190,39 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Granskog, fuktigt.</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>Granlåga.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101621434</v>
+        <v>101775134</v>
       </c>
       <c r="B41" t="n">
-        <v>94121</v>
+        <v>94829</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5211,45 +5231,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>906</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Västlig fingerfliksmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Kurzia trichoclados</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Müll.Frib.) Grolle</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundsvalen, N-sidan, Jmt</t>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>390604.1747182368</v>
+        <v>390677.9687408432</v>
       </c>
       <c r="R41" t="n">
-        <v>7061513.082409594</v>
+        <v>7061523.862175957</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5291,155 +5307,32 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Projektet Northern hepatic mat</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Granskog, fuktigt.</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Granlåga.</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>101775134</v>
-      </c>
-      <c r="B42" t="n">
-        <v>94829</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>906</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Västlig fingerfliksmossa</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Kurzia trichoclados</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Müll.Frib.) Grolle</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>390677.9687408432</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7061523.862175957</v>
-      </c>
-      <c r="S42" t="n">
-        <v>25</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Projektet Northern hepatic mat</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Tomas Hallingbäck</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101624404</v>
+        <v>101621434</v>
       </c>
       <c r="B2" t="n">
-        <v>93372</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>535</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +710,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
+          <t>Sundsvalen, N-sidan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389605.3386216339</v>
+        <v>390604</v>
       </c>
       <c r="R2" t="n">
-        <v>7061466.467316464</v>
+        <v>7061513</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +764,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bäckravin med granskog.</t>
+          <t>Granskog, fuktigt.</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bergvägg.</t>
+          <t>Granlåga.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,22 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Fredrik Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101775130</v>
+        <v>103566192</v>
       </c>
       <c r="B3" t="n">
-        <v>92665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2363</v>
+        <v>283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå stjärnmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mnium blyttii</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bruch &amp; Schimp.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389555.3168116992</v>
+        <v>389472</v>
       </c>
       <c r="R3" t="n">
-        <v>7061473.991141472</v>
+        <v>7061433</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,27 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,66 +868,66 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Grankvistar</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101775139</v>
+        <v>118378088</v>
       </c>
       <c r="B4" t="n">
-        <v>93159</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2819</v>
+        <v>310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389642.5643667446</v>
+        <v>389534</v>
       </c>
       <c r="R4" t="n">
-        <v>7061462.057225592</v>
+        <v>7061458</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,27 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,73 +970,69 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101624453</v>
+        <v>118378039</v>
       </c>
       <c r="B5" t="n">
-        <v>93159</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2819</v>
+        <v>492</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>389605.3386216339</v>
+        <v>390411</v>
       </c>
       <c r="R5" t="n">
-        <v>7061466.467316464</v>
+        <v>7061551</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,22 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,85 +1070,75 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bäckravin med granskog.</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bergvägg.</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Fredrik Larsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102571913</v>
+        <v>101624404</v>
       </c>
       <c r="B6" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>918</v>
+        <v>535</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
+          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>389580.0977153061</v>
+        <v>389605</v>
       </c>
       <c r="R6" t="n">
-        <v>7061470.014957813</v>
+        <v>7061466</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,22 +1162,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,50 +1180,35 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bäckravin med granskog.</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bergvägg.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+          <t>Leif Appelgren, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102571916</v>
+        <v>103566149</v>
       </c>
       <c r="B7" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,40 +1216,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1249</v>
+        <v>735</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389580.0977153061</v>
+        <v>390608</v>
       </c>
       <c r="R7" t="n">
-        <v>7061470.014957813</v>
+        <v>7061565</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1375,121 +1273,82 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102583100</v>
+        <v>103566189</v>
       </c>
       <c r="B8" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2813</v>
+        <v>735</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389560.3402391833</v>
+        <v>389379</v>
       </c>
       <c r="R8" t="n">
-        <v>7061464.927578781</v>
+        <v>7061454</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,22 +1372,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,90 +1386,68 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>ravin</t>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102650204</v>
+        <v>118378021</v>
       </c>
       <c r="B9" t="n">
-        <v>78610</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81013</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>264143</v>
+        <v>735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brittisk torsklav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Peltigera britannica</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>Flot. ex Körb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>389623.6803783567</v>
+        <v>389551</v>
       </c>
       <c r="R9" t="n">
-        <v>7061456.494554701</v>
+        <v>7061475</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1650,108 +1477,79 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Andra moderna lokalen i Sverige. Dellokal 2 i Sundsvalen. Arten är även känd från Skäckerfjällen. Västlig och oceanisk art som endast var känd från Västergötland, första halvan av 1900-talet.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Granskog i ravin.</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Nordvänd skuggig, fuktig lodyta.</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102911996</v>
+        <v>118378108</v>
       </c>
       <c r="B10" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81013</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>389597.9541165999</v>
+        <v>389432</v>
       </c>
       <c r="R10" t="n">
-        <v>7061433.394440808</v>
+        <v>7061449</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1778,22 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1802,34 +1590,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Maya Edlund, Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103566189</v>
+        <v>102571913</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,37 +1619,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>735</v>
+        <v>918</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>389378.4129099908</v>
+        <v>389580</v>
       </c>
       <c r="R11" t="n">
-        <v>7061454.398509734</v>
+        <v>7061470</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1891,22 +1676,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,38 +1690,49 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103566194</v>
+        <v>103566174</v>
       </c>
       <c r="B12" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1978,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>389472.0326748123</v>
+        <v>389653</v>
       </c>
       <c r="R12" t="n">
-        <v>7061433.793106548</v>
+        <v>7061468</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2011,21 +1797,11 @@
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2037,7 +1813,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ved i rothåla , rönn?</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2055,37 +1831,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103566195</v>
+        <v>103566182</v>
       </c>
       <c r="B13" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2095,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>389472.0326748123</v>
+        <v>389508</v>
       </c>
       <c r="R13" t="n">
-        <v>7061433.793106548</v>
+        <v>7061484</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2128,21 +1899,11 @@
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2154,7 +1915,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2172,53 +1933,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103566180</v>
+        <v>102911996</v>
       </c>
       <c r="B14" t="n">
-        <v>73691</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6486</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>389508.0549679111</v>
+        <v>389598</v>
       </c>
       <c r="R14" t="n">
-        <v>7061484.085756798</v>
+        <v>7061433</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2242,22 +2001,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,76 +2015,70 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Rothåla gran</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Maya Edlund, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103566174</v>
+        <v>102911954</v>
       </c>
       <c r="B15" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>389652.1147487718</v>
+        <v>390406</v>
       </c>
       <c r="R15" t="n">
-        <v>7061467.94565714</v>
+        <v>7061546</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2359,22 +2102,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2383,38 +2116,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Ved i rothåla , rönn?</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103566191</v>
+        <v>118378107</v>
       </c>
       <c r="B16" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,37 +2146,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>389472.0326748123</v>
+        <v>389435</v>
       </c>
       <c r="R16" t="n">
-        <v>7061433.793106548</v>
+        <v>7061405</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2479,21 +2203,11 @@
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2505,71 +2219,69 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103566183</v>
+        <v>102571916</v>
       </c>
       <c r="B17" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>389508.0549679111</v>
+        <v>389580</v>
       </c>
       <c r="R17" t="n">
-        <v>7061484.085756798</v>
+        <v>7061470</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2593,22 +2305,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2617,60 +2319,71 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103566193</v>
+        <v>103566191</v>
       </c>
       <c r="B18" t="n">
-        <v>79097</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228885</v>
+        <v>1249</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granpensellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gyalideopsis piceicola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Vězda &amp; Poelt</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2680,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>389472.0326748123</v>
+        <v>389472</v>
       </c>
       <c r="R18" t="n">
-        <v>7061433.793106548</v>
+        <v>7061433</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2713,21 +2426,11 @@
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2739,7 +2442,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Grankvistar</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2757,53 +2460,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103566182</v>
+        <v>118378032</v>
       </c>
       <c r="B19" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>1461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>389508.0549679111</v>
+        <v>390053</v>
       </c>
       <c r="R19" t="n">
-        <v>7061484.085756798</v>
+        <v>7061464</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2827,22 +2525,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2856,33 +2544,28 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103566178</v>
+        <v>118378085</v>
       </c>
       <c r="B20" t="n">
-        <v>73624</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2890,37 +2573,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1776</v>
+        <v>1461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>389508.0549679111</v>
+        <v>389631</v>
       </c>
       <c r="R20" t="n">
-        <v>7061484.085756798</v>
+        <v>7061464</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2947,21 +2630,11 @@
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2973,55 +2646,55 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Grangren</t>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103566197</v>
+        <v>103566181</v>
       </c>
       <c r="B21" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3031,10 +2704,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>389472.0326748123</v>
+        <v>389508</v>
       </c>
       <c r="R21" t="n">
-        <v>7061433.793106548</v>
+        <v>7061484</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3064,21 +2737,11 @@
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3090,7 +2753,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3108,15 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103566184</v>
+        <v>103566194</v>
       </c>
       <c r="B22" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,21 +2782,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3148,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>389508.0549679111</v>
+        <v>389472</v>
       </c>
       <c r="R22" t="n">
-        <v>7061484.085756798</v>
+        <v>7061433</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3181,19 +2839,9 @@
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3225,53 +2873,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103566176</v>
+        <v>118378034</v>
       </c>
       <c r="B23" t="n">
-        <v>73701</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>389652.1147487718</v>
+        <v>390082</v>
       </c>
       <c r="R23" t="n">
-        <v>7061467.94565714</v>
+        <v>7061482</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3295,22 +2938,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3324,68 +2957,63 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Rönn</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103566192</v>
+        <v>103566148</v>
       </c>
       <c r="B24" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83315</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>283</v>
+        <v>1469</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>389472.0326748123</v>
+        <v>390101</v>
       </c>
       <c r="R24" t="n">
-        <v>7061433.793106548</v>
+        <v>7061482</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3412,22 +3040,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3441,7 +3059,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Grankvistar</t>
+          <t>Björkhögstubbe</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3452,22 +3070,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>106652352</v>
+        <v>103566176</v>
       </c>
       <c r="B25" t="n">
-        <v>73624</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83315</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,40 +3088,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1776</v>
+        <v>1469</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jormlien, Frostviken, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>389539.3475003318</v>
+        <v>389653</v>
       </c>
       <c r="R25" t="n">
-        <v>7061475.437699966</v>
+        <v>7061468</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3535,64 +3145,44 @@
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Oceanisk grannaturskog.</t>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Rönn</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118378021</v>
+        <v>115808940</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83315</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,37 +3190,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>735</v>
+        <v>1469</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalens nordsluttning, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>389551</v>
+        <v>389685</v>
       </c>
       <c r="R26" t="n">
-        <v>7061475</v>
+        <v>7061500</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3654,12 +3247,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3668,60 +3266,56 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>granbas</t>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118378027</v>
+        <v>118378042</v>
       </c>
       <c r="B27" t="n">
-        <v>74605</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83315</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1469</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3731,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>389582</v>
+        <v>390411</v>
       </c>
       <c r="R27" t="n">
-        <v>7061446</v>
+        <v>7061551</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3769,11 +3363,6 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3785,7 +3374,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3803,50 +3392,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118378022</v>
+        <v>102911949</v>
       </c>
       <c r="B28" t="n">
-        <v>74417</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75421</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6428</v>
+        <v>1776</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>389551</v>
+        <v>390406</v>
       </c>
       <c r="R28" t="n">
-        <v>7061475</v>
+        <v>7061546</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3887,76 +3474,82 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118378086</v>
+        <v>103566178</v>
       </c>
       <c r="B29" t="n">
-        <v>78582</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75421</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6450</v>
+        <v>1776</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>389615</v>
+        <v>389508</v>
       </c>
       <c r="R29" t="n">
-        <v>7061456</v>
+        <v>7061484</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3999,68 +3592,66 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>Grangren</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118378115</v>
+        <v>106652352</v>
       </c>
       <c r="B30" t="n">
-        <v>79575</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75421</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>1776</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jormlien, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>389580</v>
+        <v>389539</v>
       </c>
       <c r="R30" t="n">
-        <v>7061470</v>
+        <v>7061476</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4101,60 +3692,60 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>rönn</t>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Oceanisk grannaturskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118378113</v>
+        <v>118378020</v>
       </c>
       <c r="B31" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75421</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1776</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4164,10 +3755,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>389580</v>
+        <v>389551</v>
       </c>
       <c r="R31" t="n">
-        <v>7061470</v>
+        <v>7061475</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4194,12 +3785,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4213,7 +3804,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4231,37 +3822,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118378024</v>
+        <v>118378115</v>
       </c>
       <c r="B32" t="n">
-        <v>74603</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6486</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4271,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>389551</v>
+        <v>389580</v>
       </c>
       <c r="R32" t="n">
-        <v>7061475</v>
+        <v>7061470</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4301,12 +3887,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4320,7 +3906,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4338,50 +3924,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118378108</v>
+        <v>102583100</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>735</v>
+        <v>2813</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>389432</v>
+        <v>389560</v>
       </c>
       <c r="R33" t="n">
-        <v>7061449</v>
+        <v>7061465</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4408,12 +3997,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4422,71 +4011,81 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>ravin</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118378088</v>
+        <v>101624453</v>
       </c>
       <c r="B34" t="n">
-        <v>74600</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96459</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>310</v>
+        <v>2819</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>389534</v>
+        <v>389605</v>
       </c>
       <c r="R34" t="n">
-        <v>7061458</v>
+        <v>7061466</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4510,12 +4109,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4524,73 +4123,74 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Bäckravin med granskog.</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Bergvägg.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Leif Appelgren, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118378106</v>
+        <v>101775139</v>
       </c>
       <c r="B35" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2819</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>389412</v>
+        <v>389642</v>
       </c>
       <c r="R35" t="n">
-        <v>7061456</v>
+        <v>7061462</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4617,12 +4217,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Projektet Northern hepatic mat</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4633,36 +4238,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118378020</v>
+        <v>118378106</v>
       </c>
       <c r="B36" t="n">
-        <v>74537</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4670,21 +4265,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1776</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4694,10 +4289,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>389551</v>
+        <v>389412</v>
       </c>
       <c r="R36" t="n">
-        <v>7061475</v>
+        <v>7061456</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4724,12 +4319,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4743,7 +4338,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4761,53 +4356,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118378028</v>
+        <v>103566195</v>
       </c>
       <c r="B37" t="n">
-        <v>77430</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>389582</v>
+        <v>389472</v>
       </c>
       <c r="R37" t="n">
-        <v>7061446</v>
+        <v>7061433</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4831,17 +4421,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,55 +4440,50 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118378085</v>
+        <v>118378022</v>
       </c>
       <c r="B38" t="n">
-        <v>74529</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1461</v>
+        <v>6428</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4913,10 +4493,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>389631</v>
+        <v>389551</v>
       </c>
       <c r="R38" t="n">
-        <v>7061464</v>
+        <v>7061475</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4943,12 +4523,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4962,12 +4542,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>lodyta</t>
-        </is>
-      </c>
-      <c r="AP38" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4985,15 +4560,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118378112</v>
+        <v>103566197</v>
       </c>
       <c r="B39" t="n">
-        <v>79610</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5001,37 +4571,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6439</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>389580</v>
+        <v>389472</v>
       </c>
       <c r="R39" t="n">
-        <v>7061470</v>
+        <v>7061433</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5074,75 +4644,66 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>101621434</v>
+        <v>118378040</v>
       </c>
       <c r="B40" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>6439</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sundsvalen, N-sidan, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>390604.1747182368</v>
+        <v>390411</v>
       </c>
       <c r="R40" t="n">
-        <v>7061513.082409594</v>
+        <v>7061551</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5166,22 +4727,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5190,79 +4741,68 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Granskog, fuktigt.</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Granlåga.</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101775134</v>
+        <v>118378027</v>
       </c>
       <c r="B41" t="n">
-        <v>94829</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>906</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Västlig fingerfliksmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Kurzia trichoclados</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Müll.Frib.) Grolle</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>390677.9687408432</v>
+        <v>389582</v>
       </c>
       <c r="R41" t="n">
-        <v>7061523.862175957</v>
+        <v>7061446</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5289,27 +4829,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5320,19 +4850,1949 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>118378086</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sundsvalens N-sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>389615</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7061456</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>118378113</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sundsvalens N-sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>389580</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7061470</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>103432381</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>390528</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7061549</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-07-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-07-24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>118378112</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sundsvalens N-sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>389580</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7061470</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>103566180</v>
+      </c>
+      <c r="B46" t="n">
+        <v>83305</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>389508</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7061484</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Rothåla gran</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118378024</v>
+      </c>
+      <c r="B47" t="n">
+        <v>83305</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sundsvalens N-sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>389551</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7061475</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118378045</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78333</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228575</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Brun svartspik</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis epithallina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sundsvalens N-sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>390743</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7061546</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>på Chaenotheca på grov gran</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>103566184</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>389508</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7061484</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118378028</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sundsvalens N-sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>389582</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7061446</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>103432374</v>
+      </c>
+      <c r="B51" t="n">
+        <v>86637</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>229848</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Refractohilum galligenum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>390528</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7061549</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2022-07-24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2022-07-24</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>stuplav</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Nephroma bellum # rönn</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>101775142</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97921</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>233219</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vågig rutlungmossa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Conocephalum salebrosum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>390389</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7061515</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Projektet Northern hepatic mat</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
           <t>Tomas Hallingbäck</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>102583094</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97921</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>233219</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vågig rutlungmossa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Conocephalum salebrosum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>389560</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7061465</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>ravin</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>101775120</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97218</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>233357</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lidvitmossa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sphagnum rubiginosum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Flatberg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>390757</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7061536</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Projektet Northern hepatic mat</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tomas Hallingbäck</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>102650188</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>264143</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Brittisk torsklav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Peltigera britannica</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>389672</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7061478</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Andra moderna lokalen för Sverige.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Granskog i ravin.</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Nordvänd skuggig, fuktig lodyta.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>102650204</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>264143</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Brittisk torsklav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Peltigera britannica</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>389623</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7061457</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Andra moderna lokalen i Sverige. Dellokal 2 i Sundsvalen. Arten är även känd från Skäckerfjällen. Västlig och oceanisk art som endast var känd från Västergötland, första halvan av 1900-talet.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Granskog i ravin.</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Nordvänd skuggig, fuktig lodyta.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>102911994</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>389598</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7061433</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Rikard Anderberg, Maya Edlund, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>103566147</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>390019</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7061472</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>118378110</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sundsvalens N-sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>389580</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7061470</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621434</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566192</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378088</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378039</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624404</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566149</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566189</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378021</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378108</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102571913</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566174</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566182</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102911996</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2132,6 +2202,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102911954</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2234,6 +2309,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378107</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2355,6 +2435,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102571916</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2457,6 +2542,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566191</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2559,6 +2649,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378032</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2666,6 +2761,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378085</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2768,6 +2868,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566181</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2870,6 +2975,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566194</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2972,6 +3082,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378034</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3074,6 +3189,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566148</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3176,6 +3296,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566176</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3287,6 +3412,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115808940</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3389,6 +3519,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378042</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3505,6 +3640,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102911949</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3607,6 +3747,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566178</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3717,6 +3862,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106652352</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3819,6 +3969,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378020</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3921,6 +4076,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378115</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4037,6 +4197,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583100</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4149,6 +4314,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624453</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4251,6 +4421,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775139</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4353,6 +4528,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378106</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4455,6 +4635,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566195</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4557,6 +4742,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378022</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4659,6 +4849,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566197</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4761,6 +4956,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378040</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4868,6 +5068,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378027</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4970,6 +5175,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378086</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5072,6 +5282,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378113</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5177,6 +5392,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103432381</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5279,6 +5499,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378112</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5381,6 +5606,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566180</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5483,6 +5713,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378024</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5590,6 +5825,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378045</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5692,6 +5932,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566184</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5799,6 +6044,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378028</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5919,6 +6169,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103432374</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6021,6 +6276,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775142</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6138,6 +6398,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583094</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6240,6 +6505,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775120</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6364,6 +6634,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102650188</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6488,6 +6763,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102650204</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6599,6 +6879,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102911994</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6696,6 +6981,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566147</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6793,8 +7083,73 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378110</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118378088</v>
+        <v>135830024</v>
       </c>
       <c r="B4" t="n">
-        <v>83302</v>
+        <v>79522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389534</v>
+        <v>390836</v>
       </c>
       <c r="R4" t="n">
-        <v>7061458</v>
+        <v>7061634</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,74 +995,69 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378088</t>
+          <t>https://artportalen.se/Sighting/135830024</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118378039</v>
+        <v>135830027</v>
       </c>
       <c r="B5" t="n">
-        <v>83298</v>
+        <v>83420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>390411</v>
+        <v>390620</v>
       </c>
       <c r="R5" t="n">
-        <v>7061551</v>
+        <v>7061569</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,78 +1107,69 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>björkhögstubbe</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378039</t>
+          <t>https://artportalen.se/Sighting/135830027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101624404</v>
+        <v>118378088</v>
       </c>
       <c r="B6" t="n">
-        <v>96705</v>
+        <v>83302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>535</v>
+        <v>310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>389605</v>
+        <v>389534</v>
       </c>
       <c r="R6" t="n">
-        <v>7061466</v>
+        <v>7061458</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,44 +1207,38 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bäckravin med granskog.</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bergvägg.</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Fredrik Larsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101624404</t>
+          <t>https://artportalen.se/Sighting/118378088</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103566149</v>
+        <v>118378039</v>
       </c>
       <c r="B7" t="n">
-        <v>81013</v>
+        <v>83298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,37 +1246,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>735</v>
+        <v>492</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>390608</v>
+        <v>390411</v>
       </c>
       <c r="R7" t="n">
-        <v>7061565</v>
+        <v>7061551</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,68 +1319,72 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566149</t>
+          <t>https://artportalen.se/Sighting/118378039</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103566189</v>
+        <v>101624404</v>
       </c>
       <c r="B8" t="n">
-        <v>81013</v>
+        <v>96705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>735</v>
+        <v>535</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389379</v>
+        <v>389605</v>
       </c>
       <c r="R8" t="n">
-        <v>7061454</v>
+        <v>7061466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,12 +1411,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,35 +1425,41 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bäckravin med granskog.</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>Bergvägg.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Leif Appelgren, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566189</t>
+          <t>https://artportalen.se/Sighting/101624404</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118378021</v>
+        <v>103566149</v>
       </c>
       <c r="B9" t="n">
         <v>81013</v>
@@ -1480,17 +1490,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>389551</v>
+        <v>390608</v>
       </c>
       <c r="R9" t="n">
-        <v>7061475</v>
+        <v>7061565</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,30 +1543,30 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378021</t>
+          <t>https://artportalen.se/Sighting/103566149</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118378108</v>
+        <v>103566189</v>
       </c>
       <c r="B10" t="n">
         <v>81013</v>
@@ -1587,17 +1597,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>389432</v>
+        <v>389379</v>
       </c>
       <c r="R10" t="n">
-        <v>7061449</v>
+        <v>7061454</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,31 +1647,36 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Rothåla gran</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378108</t>
+          <t>https://artportalen.se/Sighting/103566189</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102571913</v>
+        <v>118378021</v>
       </c>
       <c r="B11" t="n">
-        <v>92721</v>
+        <v>81013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,37 +1684,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>918</v>
+        <v>735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>389580</v>
+        <v>389551</v>
       </c>
       <c r="R11" t="n">
-        <v>7061470</v>
+        <v>7061475</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1740,92 +1752,76 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102571913</t>
+          <t>https://artportalen.se/Sighting/118378021</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103566174</v>
+        <v>118378108</v>
       </c>
       <c r="B12" t="n">
-        <v>81312</v>
+        <v>81013</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>735</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>389653</v>
+        <v>389432</v>
       </c>
       <c r="R12" t="n">
-        <v>7061468</v>
+        <v>7061449</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,74 +1861,69 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Ved i rothåla , rönn?</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566174</t>
+          <t>https://artportalen.se/Sighting/118378108</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103566182</v>
+        <v>135830026</v>
       </c>
       <c r="B13" t="n">
-        <v>81312</v>
+        <v>81125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>735</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>389508</v>
+        <v>390620</v>
       </c>
       <c r="R13" t="n">
-        <v>7061484</v>
+        <v>7061569</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1956,12 +1947,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,77 +1973,69 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Rothåla gran</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566182</t>
+          <t>https://artportalen.se/Sighting/135830026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102911996</v>
+        <v>135830028</v>
       </c>
       <c r="B14" t="n">
-        <v>91905</v>
+        <v>81125</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>735</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>389598</v>
+        <v>390604</v>
       </c>
       <c r="R14" t="n">
-        <v>7061433</v>
+        <v>7061567</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,12 +2059,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,34 +2083,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Maya Edlund, Ola Hammarström</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911996</t>
+          <t>https://artportalen.se/Sighting/135830028</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102911954</v>
+        <v>102571913</v>
       </c>
       <c r="B15" t="n">
-        <v>91923</v>
+        <v>92721</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,21 +2117,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>918</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2138,14 +2140,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>390406</v>
+        <v>389580</v>
       </c>
       <c r="R15" t="n">
-        <v>7061546</v>
+        <v>7061470</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2190,68 +2192,88 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
+          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911954</t>
+          <t>https://artportalen.se/Sighting/102571913</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118378107</v>
+        <v>103566174</v>
       </c>
       <c r="B16" t="n">
-        <v>91923</v>
+        <v>81312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>389435</v>
+        <v>389653</v>
       </c>
       <c r="R16" t="n">
-        <v>7061405</v>
+        <v>7061468</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2294,74 +2316,71 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Ved i rothåla , rönn?</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378107</t>
+          <t>https://artportalen.se/Sighting/103566174</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102571916</v>
+        <v>103566182</v>
       </c>
       <c r="B17" t="n">
-        <v>79486</v>
+        <v>81312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1249</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>389580</v>
+        <v>389508</v>
       </c>
       <c r="R17" t="n">
-        <v>7061470</v>
+        <v>7061484</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2385,12 +2404,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2399,92 +2418,79 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102571916</t>
+          <t>https://artportalen.se/Sighting/103566182</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103566191</v>
+        <v>102911996</v>
       </c>
       <c r="B18" t="n">
-        <v>79486</v>
+        <v>91905</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1249</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>389472</v>
+        <v>389598</v>
       </c>
       <c r="R18" t="n">
         <v>7061433</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2508,12 +2514,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,38 +2528,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Maya Edlund, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566191</t>
+          <t>https://artportalen.se/Sighting/102911996</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118378032</v>
+        <v>102911954</v>
       </c>
       <c r="B19" t="n">
-        <v>75413</v>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2561,34 +2563,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1461</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>390053</v>
+        <v>390406</v>
       </c>
       <c r="R19" t="n">
-        <v>7061464</v>
+        <v>7061546</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2629,38 +2634,34 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>lodyta</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378032</t>
+          <t>https://artportalen.se/Sighting/102911954</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118378085</v>
+        <v>118378107</v>
       </c>
       <c r="B20" t="n">
-        <v>75413</v>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1461</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2692,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>389631</v>
+        <v>389435</v>
       </c>
       <c r="R20" t="n">
-        <v>7061464</v>
+        <v>7061405</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2741,12 +2742,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>lodyta</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2763,54 +2759,57 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378085</t>
+          <t>https://artportalen.se/Sighting/118378107</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103566181</v>
+        <v>102571916</v>
       </c>
       <c r="B21" t="n">
-        <v>83312</v>
+        <v>79486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>389508</v>
+        <v>389580</v>
       </c>
       <c r="R21" t="n">
-        <v>7061484</v>
+        <v>7061470</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2834,12 +2833,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2848,60 +2847,76 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566181</t>
+          <t>https://artportalen.se/Sighting/102571916</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103566194</v>
+        <v>103566191</v>
       </c>
       <c r="B22" t="n">
-        <v>83312</v>
+        <v>79486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2977,38 +2992,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566194</t>
+          <t>https://artportalen.se/Sighting/103566191</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118378034</v>
+        <v>118378032</v>
       </c>
       <c r="B23" t="n">
-        <v>83312</v>
+        <v>75413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3018,10 +3033,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>390082</v>
+        <v>390053</v>
       </c>
       <c r="R23" t="n">
-        <v>7061482</v>
+        <v>7061464</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3067,7 +3082,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3084,16 +3099,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378034</t>
+          <t>https://artportalen.se/Sighting/118378032</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103566148</v>
+        <v>118378085</v>
       </c>
       <c r="B24" t="n">
-        <v>83315</v>
+        <v>75413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3101,37 +3116,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1469</v>
+        <v>1461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>390101</v>
+        <v>389631</v>
       </c>
       <c r="R24" t="n">
-        <v>7061482</v>
+        <v>7061464</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3155,12 +3170,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,55 +3189,60 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Björkhögstubbe</t>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566148</t>
+          <t>https://artportalen.se/Sighting/118378085</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103566176</v>
+        <v>103566181</v>
       </c>
       <c r="B25" t="n">
-        <v>83315</v>
+        <v>83312</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3252,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>389653</v>
+        <v>389508</v>
       </c>
       <c r="R25" t="n">
-        <v>7061468</v>
+        <v>7061484</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3281,7 +3301,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Rönn</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3298,54 +3318,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566176</t>
+          <t>https://artportalen.se/Sighting/103566181</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115808940</v>
+        <v>103566194</v>
       </c>
       <c r="B26" t="n">
-        <v>83315</v>
+        <v>83312</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sundsvalens nordsluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>389685</v>
+        <v>389472</v>
       </c>
       <c r="R26" t="n">
-        <v>7061500</v>
+        <v>7061433</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,72 +3397,66 @@
           <t>2022-07-25</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115808940</t>
+          <t>https://artportalen.se/Sighting/103566194</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118378042</v>
+        <v>118378034</v>
       </c>
       <c r="B27" t="n">
-        <v>83315</v>
+        <v>83312</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3455,10 +3466,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>390411</v>
+        <v>390082</v>
       </c>
       <c r="R27" t="n">
-        <v>7061551</v>
+        <v>7061482</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3504,7 +3515,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3521,57 +3532,54 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378042</t>
+          <t>https://artportalen.se/Sighting/118378034</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102911949</v>
+        <v>135830030</v>
       </c>
       <c r="B28" t="n">
-        <v>75421</v>
+        <v>83433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1776</v>
+        <v>1467</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>390406</v>
+        <v>390604</v>
       </c>
       <c r="R28" t="n">
-        <v>7061546</v>
+        <v>7061561</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3595,12 +3603,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,49 +3627,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911949</t>
+          <t>https://artportalen.se/Sighting/135830030</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103566178</v>
+        <v>103566148</v>
       </c>
       <c r="B29" t="n">
-        <v>75421</v>
+        <v>83315</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,34 +3661,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1776</v>
+        <v>1469</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>389508</v>
+        <v>390101</v>
       </c>
       <c r="R29" t="n">
-        <v>7061484</v>
+        <v>7061482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3713,12 +3715,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,7 +3734,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Grangren</t>
+          <t>Björkhögstubbe</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3743,22 +3745,22 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566178</t>
+          <t>https://artportalen.se/Sighting/103566148</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>106652352</v>
+        <v>103566176</v>
       </c>
       <c r="B30" t="n">
-        <v>75421</v>
+        <v>83315</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,40 +3768,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1776</v>
+        <v>1469</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jormlien, Frostviken, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>389539</v>
+        <v>389653</v>
       </c>
       <c r="R30" t="n">
-        <v>7061476</v>
+        <v>7061468</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3837,43 +3836,38 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Oceanisk grannaturskog.</t>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Rönn</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106652352</t>
+          <t>https://artportalen.se/Sighting/103566176</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118378020</v>
+        <v>115808940</v>
       </c>
       <c r="B31" t="n">
-        <v>75421</v>
+        <v>83315</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3881,37 +3875,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1776</v>
+        <v>1469</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalens nordsluttning, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>389551</v>
+        <v>389685</v>
       </c>
       <c r="R31" t="n">
-        <v>7061475</v>
+        <v>7061500</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3935,12 +3932,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,60 +3951,61 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>granbas</t>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378020</t>
+          <t>https://artportalen.se/Sighting/115808940</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118378115</v>
+        <v>118378042</v>
       </c>
       <c r="B32" t="n">
-        <v>80433</v>
+        <v>83315</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>1469</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4012,10 +4015,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>389580</v>
+        <v>390411</v>
       </c>
       <c r="R32" t="n">
-        <v>7061470</v>
+        <v>7061551</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4042,12 +4045,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4061,7 +4064,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4078,59 +4081,54 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378115</t>
+          <t>https://artportalen.se/Sighting/118378042</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>102583100</v>
+        <v>102911949</v>
       </c>
       <c r="B33" t="n">
-        <v>96350</v>
+        <v>75421</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2813</v>
+        <v>1776</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>389560</v>
+        <v>390406</v>
       </c>
       <c r="R33" t="n">
-        <v>7061465</v>
+        <v>7061546</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4175,79 +4173,80 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>ravin</t>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102583100</t>
+          <t>https://artportalen.se/Sighting/102911949</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101624453</v>
+        <v>103566178</v>
       </c>
       <c r="B34" t="n">
-        <v>96459</v>
+        <v>75421</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2819</v>
+        <v>1776</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>389605</v>
+        <v>389508</v>
       </c>
       <c r="R34" t="n">
-        <v>7061466</v>
+        <v>7061484</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4274,12 +4273,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4288,79 +4287,76 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Bäckravin med granskog.</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bergvägg.</t>
+          <t>Grangren</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Fredrik Larsson</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101624453</t>
+          <t>https://artportalen.se/Sighting/103566178</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101775139</v>
+        <v>106652352</v>
       </c>
       <c r="B35" t="n">
-        <v>96459</v>
+        <v>75421</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2819</v>
+        <v>1776</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Sundsvalen, Jormlien, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>389642</v>
+        <v>389539</v>
       </c>
       <c r="R35" t="n">
-        <v>7061462</v>
+        <v>7061476</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4387,17 +4383,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4406,33 +4397,43 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Oceanisk grannaturskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101775139</t>
+          <t>https://artportalen.se/Sighting/106652352</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118378106</v>
+        <v>118378020</v>
       </c>
       <c r="B36" t="n">
-        <v>79327</v>
+        <v>75421</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4440,21 +4441,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1776</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4464,10 +4465,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>389412</v>
+        <v>389551</v>
       </c>
       <c r="R36" t="n">
-        <v>7061456</v>
+        <v>7061475</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4494,12 +4495,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4513,7 +4514,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4530,54 +4531,54 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378106</t>
+          <t>https://artportalen.se/Sighting/118378020</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103566195</v>
+        <v>118378115</v>
       </c>
       <c r="B37" t="n">
-        <v>75300</v>
+        <v>80433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6428</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>389472</v>
+        <v>389580</v>
       </c>
       <c r="R37" t="n">
-        <v>7061433</v>
+        <v>7061470</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4620,33 +4621,33 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566195</t>
+          <t>https://artportalen.se/Sighting/118378115</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118378022</v>
+        <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>75300</v>
+        <v>97933</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4654,37 +4655,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6428</v>
+        <v>2389</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>389551</v>
+        <v>390836</v>
       </c>
       <c r="R38" t="n">
-        <v>7061475</v>
+        <v>7061634</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4708,12 +4709,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4724,36 +4735,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>granbas</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378022</t>
+          <t>https://artportalen.se/Sighting/135830025</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>103566197</v>
+        <v>102583100</v>
       </c>
       <c r="B39" t="n">
-        <v>83290</v>
+        <v>96350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,37 +4767,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6439</v>
+        <v>2813</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>389472</v>
+        <v>389560</v>
       </c>
       <c r="R39" t="n">
-        <v>7061433</v>
+        <v>7061465</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4815,12 +4829,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4829,38 +4843,44 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Gran</t>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>ravin</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566197</t>
+          <t>https://artportalen.se/Sighting/102583100</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118378040</v>
+        <v>101624453</v>
       </c>
       <c r="B40" t="n">
-        <v>83290</v>
+        <v>96459</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4868,37 +4888,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6439</v>
+        <v>2819</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>390411</v>
+        <v>389605</v>
       </c>
       <c r="R40" t="n">
-        <v>7061551</v>
+        <v>7061466</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4922,12 +4946,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4936,73 +4960,79 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Bäckravin med granskog.</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>Bergvägg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Leif Appelgren, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378040</t>
+          <t>https://artportalen.se/Sighting/101624453</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118378027</v>
+        <v>101775139</v>
       </c>
       <c r="B41" t="n">
-        <v>83307</v>
+        <v>96459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>2819</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>389582</v>
+        <v>389642</v>
       </c>
       <c r="R41" t="n">
-        <v>7061446</v>
+        <v>7061462</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5029,17 +5059,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>mikroskoperad</t>
+          <t>Projektet Northern hepatic mat</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5050,58 +5080,53 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378027</t>
+          <t>https://artportalen.se/Sighting/101775139</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118378086</v>
+        <v>118378106</v>
       </c>
       <c r="B42" t="n">
-        <v>79413</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5111,7 +5136,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>389615</v>
+        <v>389412</v>
       </c>
       <c r="R42" t="n">
         <v>7061456</v>
@@ -5160,7 +5185,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5177,54 +5202,54 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378086</t>
+          <t>https://artportalen.se/Sighting/118378106</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118378113</v>
+        <v>103566195</v>
       </c>
       <c r="B43" t="n">
-        <v>80432</v>
+        <v>75300</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>389580</v>
+        <v>389472</v>
       </c>
       <c r="R43" t="n">
-        <v>7061470</v>
+        <v>7061433</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5267,33 +5292,33 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378113</t>
+          <t>https://artportalen.se/Sighting/103566195</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>103432381</v>
+        <v>118378022</v>
       </c>
       <c r="B44" t="n">
-        <v>80461</v>
+        <v>75300</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5301,37 +5326,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6428</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>390528</v>
+        <v>389551</v>
       </c>
       <c r="R44" t="n">
-        <v>7061549</v>
+        <v>7061475</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5358,12 +5380,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5372,38 +5394,38 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103432381</t>
+          <t>https://artportalen.se/Sighting/118378022</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118378112</v>
+        <v>103566197</v>
       </c>
       <c r="B45" t="n">
-        <v>80468</v>
+        <v>83290</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5411,37 +5433,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6439</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>389580</v>
+        <v>389472</v>
       </c>
       <c r="R45" t="n">
-        <v>7061470</v>
+        <v>7061433</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5484,71 +5506,71 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378112</t>
+          <t>https://artportalen.se/Sighting/103566197</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>103566180</v>
+        <v>118378040</v>
       </c>
       <c r="B46" t="n">
-        <v>83305</v>
+        <v>83290</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6486</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>389508</v>
+        <v>390411</v>
       </c>
       <c r="R46" t="n">
-        <v>7061484</v>
+        <v>7061551</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5572,12 +5594,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5591,55 +5613,55 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566180</t>
+          <t>https://artportalen.se/Sighting/118378040</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118378024</v>
+        <v>118378027</v>
       </c>
       <c r="B47" t="n">
-        <v>83305</v>
+        <v>83307</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5649,10 +5671,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>389551</v>
+        <v>389582</v>
       </c>
       <c r="R47" t="n">
-        <v>7061475</v>
+        <v>7061446</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5687,6 +5709,11 @@
           <t>2022-07-27</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5698,7 +5725,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5715,16 +5742,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378024</t>
+          <t>https://artportalen.se/Sighting/118378027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118378045</v>
+        <v>118378086</v>
       </c>
       <c r="B48" t="n">
-        <v>78333</v>
+        <v>79413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5732,21 +5759,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228575</v>
+        <v>6450</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brun svartspik</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis epithallina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5756,10 +5783,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>390743</v>
+        <v>389615</v>
       </c>
       <c r="R48" t="n">
-        <v>7061546</v>
+        <v>7061456</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5786,12 +5813,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5805,12 +5832,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>på Chaenotheca på grov gran</t>
-        </is>
-      </c>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>block</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5827,16 +5849,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378045</t>
+          <t>https://artportalen.se/Sighting/118378086</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103566184</v>
+        <v>118378113</v>
       </c>
       <c r="B49" t="n">
-        <v>78339</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5844,37 +5866,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>389508</v>
+        <v>389580</v>
       </c>
       <c r="R49" t="n">
-        <v>7061484</v>
+        <v>7061470</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5917,71 +5939,71 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566184</t>
+          <t>https://artportalen.se/Sighting/118378113</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118378028</v>
+        <v>135830023</v>
       </c>
       <c r="B50" t="n">
-        <v>78339</v>
+        <v>79697</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>6459</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>389582</v>
+        <v>390836</v>
       </c>
       <c r="R50" t="n">
-        <v>7061446</v>
+        <v>7061634</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6005,17 +6027,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6026,53 +6053,53 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378028</t>
+          <t>https://artportalen.se/Sighting/135830023</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103432374</v>
+        <v>103432381</v>
       </c>
       <c r="B51" t="n">
-        <v>86637</v>
+        <v>80461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229848</v>
+        <v>6462</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Refractohilum galligenum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6137,26 +6164,6 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>stuplav</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Nephroma bellum # rönn</t>
-        </is>
-      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -6171,16 +6178,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103432374</t>
+          <t>https://artportalen.se/Sighting/103432381</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>101775142</v>
+        <v>118378112</v>
       </c>
       <c r="B52" t="n">
-        <v>97921</v>
+        <v>80468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6188,34 +6195,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>233219</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågig rutlungmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Conocephalum salebrosum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>390389</v>
+        <v>389580</v>
       </c>
       <c r="R52" t="n">
-        <v>7061515</v>
+        <v>7061470</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6242,17 +6249,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6263,73 +6265,74 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101775142</t>
+          <t>https://artportalen.se/Sighting/118378112</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>102583094</v>
+        <v>103566180</v>
       </c>
       <c r="B53" t="n">
-        <v>97921</v>
+        <v>83305</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>233219</v>
+        <v>6486</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågig rutlungmossa</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Conocephalum salebrosum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>389560</v>
+        <v>389508</v>
       </c>
       <c r="R53" t="n">
-        <v>7061465</v>
+        <v>7061484</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6353,12 +6356,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6367,49 +6370,38 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>ravin</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>Rikard Anderberg</t>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102583094</t>
+          <t>https://artportalen.se/Sighting/103566180</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>101775120</v>
+        <v>118378024</v>
       </c>
       <c r="B54" t="n">
-        <v>97218</v>
+        <v>83305</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6417,34 +6409,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>233357</v>
+        <v>6486</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lidvitmossa</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sphagnum rubiginosum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Flatberg</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>390757</v>
+        <v>389551</v>
       </c>
       <c r="R54" t="n">
-        <v>7061536</v>
+        <v>7061475</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6471,17 +6463,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6492,77 +6479,71 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101775120</t>
+          <t>https://artportalen.se/Sighting/118378024</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102650188</v>
+        <v>118378045</v>
       </c>
       <c r="B55" t="n">
-        <v>80474</v>
+        <v>78333</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>264143</v>
+        <v>228575</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brittisk torsklav</t>
+          <t>Brun svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Peltigera britannica</t>
+          <t>Chaenothecopsis epithallina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>389672</v>
+        <v>390743</v>
       </c>
       <c r="R55" t="n">
-        <v>7061478</v>
+        <v>7061546</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6597,104 +6578,87 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Andra moderna lokalen för Sverige.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Granskog i ravin.</t>
-        </is>
-      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Nordvänd skuggig, fuktig lodyta.</t>
+          <t>på Chaenotheca på grov gran</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102650188</t>
+          <t>https://artportalen.se/Sighting/118378045</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>102650204</v>
+        <v>103566184</v>
       </c>
       <c r="B56" t="n">
-        <v>80474</v>
+        <v>78339</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>264143</v>
+        <v>228579</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brittisk torsklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Peltigera britannica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>389623</v>
+        <v>389508</v>
       </c>
       <c r="R56" t="n">
-        <v>7061457</v>
+        <v>7061484</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6718,17 +6682,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Andra moderna lokalen i Sverige. Dellokal 2 i Sundsvalen. Arten är även känd från Skäckerfjällen. Västlig och oceanisk art som endast var känd från Västergötland, första halvan av 1900-talet.</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6737,77 +6696,73 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Granskog i ravin.</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Nordvänd skuggig, fuktig lodyta.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102650204</t>
+          <t>https://artportalen.se/Sighting/103566184</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>102911994</v>
+        <v>118378028</v>
       </c>
       <c r="B57" t="n">
-        <v>79497</v>
+        <v>78339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6000492</v>
+        <v>228579</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Protoparmelia ochrococca</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) P.M.Jørg. et al.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>389598</v>
+        <v>389582</v>
       </c>
       <c r="R57" t="n">
-        <v>7061433</v>
+        <v>7061446</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6842,88 +6797,85 @@
           <t>2022-07-27</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
+      <c r="AO57" t="inlineStr">
         <is>
           <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Rikard Anderberg, Maya Edlund, Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911994</t>
+          <t>https://artportalen.se/Sighting/118378028</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>103566147</v>
+        <v>103432374</v>
       </c>
       <c r="B58" t="n">
-        <v>79497</v>
+        <v>86637</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6000492</v>
+        <v>229848</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Protoparmelia ochrococca</t>
+          <t>Refractohilum galligenum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) P.M.Jørg. et al.</t>
+          <t>D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>390019</v>
+        <v>390528</v>
       </c>
       <c r="R58" t="n">
-        <v>7061472</v>
+        <v>7061549</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6947,12 +6899,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6961,68 +6913,93 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>stuplav</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Nephroma bellum # rönn</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+          <t>Robin Isaksson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566147</t>
+          <t>https://artportalen.se/Sighting/103432374</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118378110</v>
+        <v>101775142</v>
       </c>
       <c r="B59" t="n">
-        <v>79497</v>
+        <v>97921</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6000492</v>
+        <v>233219</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vågig rutlungmossa</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Protoparmelia ochrococca</t>
+          <t>Conocephalum salebrosum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) P.M.Jørg. et al.</t>
+          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>389580</v>
+        <v>390389</v>
       </c>
       <c r="R59" t="n">
-        <v>7061470</v>
+        <v>7061515</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7049,12 +7026,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Projektet Northern hepatic mat</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7065,25 +7047,948 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775142</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>102583094</v>
+      </c>
+      <c r="B60" t="n">
+        <v>97921</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>233219</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vågig rutlungmossa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Conocephalum salebrosum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>389560</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7061465</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>ravin</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583094</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>101775120</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97218</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>233357</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lidvitmossa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sphagnum rubiginosum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Flatberg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>390757</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7061536</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Projektet Northern hepatic mat</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tomas Hallingbäck</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101775120</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>102650188</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>264143</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Brittisk torsklav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Peltigera britannica</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>389672</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7061478</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Andra moderna lokalen för Sverige.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Granskog i ravin.</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Nordvänd skuggig, fuktig lodyta.</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102650188</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>102650204</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>264143</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Brittisk torsklav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Peltigera britannica</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>389623</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7061457</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Andra moderna lokalen i Sverige. Dellokal 2 i Sundsvalen. Arten är även känd från Skäckerfjällen. Västlig och oceanisk art som endast var känd från Västergötland, första halvan av 1900-talet.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Granskog i ravin.</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Nordvänd skuggig, fuktig lodyta.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102650204</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135830031</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80573</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>264143</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Brittisk torsklav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Peltigera britannica</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>389640</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7061467</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Återfynd på känd lokal</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135830031</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>102911994</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>389598</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7061433</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Rikard Anderberg, Maya Edlund, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102911994</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>103566147</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>390019</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7061472</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566147</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>118378110</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Sundsvalens N-sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>389580</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7061470</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118378110</t>
         </is>
@@ -7149,6 +8054,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97933</v>
+        <v>97935</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135830024</v>
       </c>
       <c r="B4" t="n">
-        <v>79522</v>
+        <v>79524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135830027</v>
       </c>
       <c r="B5" t="n">
-        <v>83420</v>
+        <v>83422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135830026</v>
       </c>
       <c r="B13" t="n">
-        <v>81125</v>
+        <v>81127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135830028</v>
       </c>
       <c r="B14" t="n">
-        <v>81125</v>
+        <v>81127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>135830030</v>
       </c>
       <c r="B28" t="n">
-        <v>83433</v>
+        <v>83435</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97935</v>
+        <v>97952</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>135830023</v>
       </c>
       <c r="B50" t="n">
-        <v>79697</v>
+        <v>79699</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135830031</v>
       </c>
       <c r="B64" t="n">
-        <v>80573</v>
+        <v>80575</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135830024</v>
       </c>
       <c r="B4" t="n">
-        <v>79524</v>
+        <v>79525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135830027</v>
       </c>
       <c r="B5" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135830026</v>
       </c>
       <c r="B13" t="n">
-        <v>81127</v>
+        <v>81128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135830028</v>
       </c>
       <c r="B14" t="n">
-        <v>81127</v>
+        <v>81128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>135830030</v>
       </c>
       <c r="B28" t="n">
-        <v>83435</v>
+        <v>83436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97952</v>
+        <v>97953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>135830023</v>
       </c>
       <c r="B50" t="n">
-        <v>79699</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135830031</v>
       </c>
       <c r="B64" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97953</v>
+        <v>97954</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97218</v>
+        <v>97392</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135830024</v>
       </c>
       <c r="B4" t="n">
-        <v>79525</v>
+        <v>79526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135830027</v>
       </c>
       <c r="B5" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135830026</v>
       </c>
       <c r="B13" t="n">
-        <v>81128</v>
+        <v>81129</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135830028</v>
       </c>
       <c r="B14" t="n">
-        <v>81128</v>
+        <v>81129</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>135830030</v>
       </c>
       <c r="B28" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97954</v>
+        <v>97955</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>135830023</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>79701</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97392</v>
+        <v>97393</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135830031</v>
       </c>
       <c r="B64" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135830024</v>
       </c>
       <c r="B4" t="n">
-        <v>79526</v>
+        <v>79530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135830027</v>
       </c>
       <c r="B5" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135830026</v>
       </c>
       <c r="B13" t="n">
-        <v>81129</v>
+        <v>81133</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135830028</v>
       </c>
       <c r="B14" t="n">
-        <v>81129</v>
+        <v>81133</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>135830030</v>
       </c>
       <c r="B28" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97955</v>
+        <v>97961</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>135830023</v>
       </c>
       <c r="B50" t="n">
-        <v>79701</v>
+        <v>79705</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97393</v>
+        <v>97399</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135830031</v>
       </c>
       <c r="B64" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135830024</v>
       </c>
       <c r="B4" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135830027</v>
       </c>
       <c r="B5" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135830026</v>
       </c>
       <c r="B13" t="n">
-        <v>81133</v>
+        <v>81134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135830028</v>
       </c>
       <c r="B14" t="n">
-        <v>81133</v>
+        <v>81134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>135830030</v>
       </c>
       <c r="B28" t="n">
-        <v>83441</v>
+        <v>83442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97961</v>
+        <v>97962</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>135830023</v>
       </c>
       <c r="B50" t="n">
-        <v>79705</v>
+        <v>79706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97399</v>
+        <v>97400</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135830031</v>
       </c>
       <c r="B64" t="n">
-        <v>80581</v>
+        <v>80582</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135830024</v>
       </c>
       <c r="B4" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135830027</v>
       </c>
       <c r="B5" t="n">
-        <v>83429</v>
+        <v>83433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135830026</v>
       </c>
       <c r="B13" t="n">
-        <v>81134</v>
+        <v>81138</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135830028</v>
       </c>
       <c r="B14" t="n">
-        <v>81134</v>
+        <v>81138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>135830030</v>
       </c>
       <c r="B28" t="n">
-        <v>83442</v>
+        <v>83446</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97962</v>
+        <v>97973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>135830023</v>
       </c>
       <c r="B50" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97400</v>
+        <v>97411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135830031</v>
       </c>
       <c r="B64" t="n">
-        <v>80582</v>
+        <v>80586</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135830024</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135830027</v>
       </c>
       <c r="B5" t="n">
-        <v>83433</v>
+        <v>83439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135830026</v>
       </c>
       <c r="B13" t="n">
-        <v>81138</v>
+        <v>81144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135830028</v>
       </c>
       <c r="B14" t="n">
-        <v>81138</v>
+        <v>81144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>135830030</v>
       </c>
       <c r="B28" t="n">
-        <v>83446</v>
+        <v>83452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97973</v>
+        <v>97986</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>135830023</v>
       </c>
       <c r="B50" t="n">
-        <v>79710</v>
+        <v>79716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97411</v>
+        <v>97424</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135830031</v>
       </c>
       <c r="B64" t="n">
-        <v>80586</v>
+        <v>80592</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97424</v>
+        <v>97425</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135830024</v>
       </c>
       <c r="B4" t="n">
-        <v>79541</v>
+        <v>79554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135830027</v>
       </c>
       <c r="B5" t="n">
-        <v>83439</v>
+        <v>83452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135830026</v>
       </c>
       <c r="B13" t="n">
-        <v>81144</v>
+        <v>81157</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135830028</v>
       </c>
       <c r="B14" t="n">
-        <v>81144</v>
+        <v>81157</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>135830030</v>
       </c>
       <c r="B28" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135830025</v>
       </c>
       <c r="B38" t="n">
-        <v>97987</v>
+        <v>98000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>135830023</v>
       </c>
       <c r="B50" t="n">
-        <v>79716</v>
+        <v>79729</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97425</v>
+        <v>97438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135830031</v>
       </c>
       <c r="B64" t="n">
-        <v>80592</v>
+        <v>80605</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1885,7 +1885,7 @@
         <v>135830026</v>
       </c>
       <c r="B13" t="n">
-        <v>81157</v>
+        <v>81158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97438</v>
+        <v>97439</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>135830031</v>
       </c>
       <c r="B64" t="n">
-        <v>80605</v>
+        <v>80606</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
